--- a/artfynd/A 72168-2021 artfynd.xlsx
+++ b/artfynd/A 72168-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 72168-2021 artfynd.xlsx
+++ b/artfynd/A 72168-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110941016</v>
+        <v>110941065</v>
       </c>
       <c r="B2" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548711.9460604276</v>
+        <v>548834</v>
       </c>
       <c r="R2" t="n">
-        <v>7263479.396998118</v>
+        <v>7263409</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>05:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>05:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110941012</v>
+        <v>110941009</v>
       </c>
       <c r="B3" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548573.3093619875</v>
+        <v>548992</v>
       </c>
       <c r="R3" t="n">
-        <v>7263612.50926474</v>
+        <v>7263409</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110941135</v>
+        <v>110941012</v>
       </c>
       <c r="B4" t="n">
-        <v>96350</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219811</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548944.5073468505</v>
+        <v>548573</v>
       </c>
       <c r="R4" t="n">
-        <v>7263599.195363902</v>
+        <v>7263613</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110941017</v>
+        <v>110941013</v>
       </c>
       <c r="B5" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548774.2050403708</v>
+        <v>548594</v>
       </c>
       <c r="R5" t="n">
-        <v>7263462.159360974</v>
+        <v>7263598</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,12 +1106,7 @@
         <v>110941014</v>
       </c>
       <c r="B6" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548640.5057085881</v>
+        <v>548641</v>
       </c>
       <c r="R6" t="n">
-        <v>7263523.485069374</v>
+        <v>7263523</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1235,37 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110940990</v>
+        <v>110941015</v>
       </c>
       <c r="B7" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548779.5143311676</v>
+        <v>548716</v>
       </c>
       <c r="R7" t="n">
-        <v>7263443.138361806</v>
+        <v>7263464</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110940989</v>
+        <v>110941016</v>
       </c>
       <c r="B8" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548716.9355782456</v>
+        <v>548712</v>
       </c>
       <c r="R8" t="n">
-        <v>7263479.480395136</v>
+        <v>7263479</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1459,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110941015</v>
+        <v>110941017</v>
       </c>
       <c r="B9" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548716.3539021927</v>
+        <v>548774</v>
       </c>
       <c r="R9" t="n">
-        <v>7263464.515245019</v>
+        <v>7263462</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110941121</v>
+        <v>110941018</v>
       </c>
       <c r="B10" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548833.604623973</v>
+        <v>548913</v>
       </c>
       <c r="R10" t="n">
-        <v>7263417.040869318</v>
+        <v>7263365</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>05:44</t>
+          <t>05:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>05:44</t>
+          <t>05:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,59 +1638,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110940982</v>
+        <v>110941120</v>
       </c>
       <c r="B11" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brånaviken, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548628.2330932645</v>
+        <v>548624</v>
       </c>
       <c r="R11" t="n">
-        <v>7263561.083319796</v>
+        <v>7263563</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1804,32 +1745,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110941132</v>
+        <v>110941121</v>
       </c>
       <c r="B12" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1844,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548779.5143311676</v>
+        <v>548834</v>
       </c>
       <c r="R12" t="n">
-        <v>7263443.138361806</v>
+        <v>7263417</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,37 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110941018</v>
+        <v>110940989</v>
       </c>
       <c r="B13" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548913.5061358479</v>
+        <v>548717</v>
       </c>
       <c r="R13" t="n">
-        <v>7263364.788817332</v>
+        <v>7263480</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>05:39</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>05:39</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,37 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110941065</v>
+        <v>110940990</v>
       </c>
       <c r="B14" t="n">
-        <v>78446</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2080</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548833.7437971227</v>
+        <v>548780</v>
       </c>
       <c r="R14" t="n">
-        <v>7263408.734450101</v>
+        <v>7263443</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>05:43</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>05:43</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,15 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110941076</v>
+        <v>110941132</v>
       </c>
       <c r="B15" t="n">
-        <v>78612</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548716.3539021927</v>
+        <v>548780</v>
       </c>
       <c r="R15" t="n">
-        <v>7263464.515245019</v>
+        <v>7263443</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,37 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110941120</v>
+        <v>110941076</v>
       </c>
       <c r="B16" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548624.0406343078</v>
+        <v>548716</v>
       </c>
       <c r="R16" t="n">
-        <v>7263563.090446088</v>
+        <v>7263464</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>05:57</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>05:57</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,15 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110941013</v>
+        <v>110940982</v>
       </c>
       <c r="B17" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,34 +2291,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brånaviken, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548593.5158002174</v>
+        <v>548628</v>
       </c>
       <c r="R17" t="n">
-        <v>7263597.891392635</v>
+        <v>7263561</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>05:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>05:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2473,6 +2393,336 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110941077</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brånaviken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>548699</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7263474</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>110941135</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brånaviken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>548945</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7263599</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>110940977</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brånaviken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>548945</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7263334</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>05:37</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>05:37</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
